--- a/artfynd/A 18689-2023 artfynd.xlsx
+++ b/artfynd/A 18689-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126014582</v>
       </c>
       <c r="B2" t="n">
-        <v>101593</v>
+        <v>101595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126014454</v>
       </c>
       <c r="B3" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2023 artfynd.xlsx
+++ b/artfynd/A 18689-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126014582</v>
       </c>
       <c r="B2" t="n">
-        <v>101595</v>
+        <v>101599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126014454</v>
       </c>
       <c r="B3" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2023 artfynd.xlsx
+++ b/artfynd/A 18689-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126014582</v>
       </c>
       <c r="B2" t="n">
-        <v>101599</v>
+        <v>101600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126014454</v>
       </c>
       <c r="B3" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2023 artfynd.xlsx
+++ b/artfynd/A 18689-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126014582</v>
       </c>
       <c r="B2" t="n">
-        <v>101600</v>
+        <v>101602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126014454</v>
       </c>
       <c r="B3" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2023 artfynd.xlsx
+++ b/artfynd/A 18689-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126014582</v>
       </c>
       <c r="B2" t="n">
-        <v>101602</v>
+        <v>101604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126014454</v>
       </c>
       <c r="B3" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2023 artfynd.xlsx
+++ b/artfynd/A 18689-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126014582</v>
       </c>
       <c r="B2" t="n">
-        <v>101604</v>
+        <v>101606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126014454</v>
       </c>
       <c r="B3" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2023 artfynd.xlsx
+++ b/artfynd/A 18689-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126014582</v>
       </c>
       <c r="B2" t="n">
-        <v>101606</v>
+        <v>101610</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126014454</v>
       </c>
       <c r="B3" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2023 artfynd.xlsx
+++ b/artfynd/A 18689-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126014582</v>
       </c>
       <c r="B2" t="n">
-        <v>101610</v>
+        <v>101613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126014454</v>
       </c>
       <c r="B3" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 18689-2023 artfynd.xlsx
+++ b/artfynd/A 18689-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126014582</v>
       </c>
       <c r="B2" t="n">
-        <v>101613</v>
+        <v>101622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126014454</v>
       </c>
       <c r="B3" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
